--- a/resources/Progetti di CS esistenti in seno a NBFC (Risposte)_TL.xlsx
+++ b/resources/Progetti di CS esistenti in seno a NBFC (Risposte)_TL.xlsx
@@ -155,7 +155,7 @@
     <t xml:space="preserve">Alpi orientali, biologia, biodiversità, farfalle, lepidotteri</t>
   </si>
   <si>
-    <t xml:space="preserve">02_Neptis</t>
+    <t xml:space="preserve">02_Neptis.png</t>
   </si>
   <si>
     <t xml:space="preserve">AlienFish</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">Ambiente, microplastiche, spiagge</t>
   </si>
   <si>
-    <t xml:space="preserve">07_guardiani</t>
+    <t xml:space="preserve">07_guardiani.png</t>
   </si>
   <si>
     <t xml:space="preserve">SOS Pinna: la Subacquea aiuta la Ricerca</t>
@@ -609,7 +609,7 @@
     <t xml:space="preserve">biodiversità marina, Mediterraneo, </t>
   </si>
   <si>
-    <t xml:space="preserve">14_sentinelledelmare</t>
+    <t xml:space="preserve">14_sentinelledelmare.png</t>
   </si>
   <si>
     <t xml:space="preserve">CLIC! Chiocciole Lumache In Città</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">Arpal e partner di progetto con contributo IMC su comunicazione e Citizen science </t>
   </si>
   <si>
-    <t xml:space="preserve">19_pinnanobilis</t>
+    <t xml:space="preserve">19_pinnanobilis.png</t>
   </si>
   <si>
     <t xml:space="preserve">PCSI - Plastic Crime Scene Investigation</t>
@@ -1095,7 +1095,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O1000"/>
-  <sheetFormatPr defaultColWidth="12.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.71484375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="120.65"/>

--- a/resources/Progetti di CS esistenti in seno a NBFC (Risposte)_TL.xlsx
+++ b/resources/Progetti di CS esistenti in seno a NBFC (Risposte)_TL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giacomoterreni/projects/homestead7/EU-CS_platform/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giacomoterreni/projects/homestead7/citizen.test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEE6B0E-B8C3-EA4D-B480-73AC8FCDCD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DC1446-0C88-9048-9EAE-93084905E8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17760" yWindow="8120" windowWidth="30720" windowHeight="17160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="2700" windowWidth="47120" windowHeight="22800" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Risposte del modulo 1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="244">
   <si>
     <t>Nome del progetto</t>
   </si>
@@ -484,9 +484,6 @@
   </si>
   <si>
     <t>https://www.framework-biodiversity.eu/</t>
-  </si>
-  <si>
-    <t>periodicamente attivo</t>
   </si>
   <si>
     <t xml:space="preserve">gestione e monitoraggio della biodiversità in agroecosistemi europei coinvolgendo gli agricoltori e la cittadinanza. Una parte del progetto prevede l'organizzazione di BioBlitz nelle aree di studio del progetto. </t>
@@ -1077,9 +1074,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1117,7 +1114,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1223,7 +1220,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1365,7 +1362,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1378,7 +1375,7 @@
   <cols>
     <col min="4" max="4" width="35.1640625" customWidth="1"/>
     <col min="5" max="5" width="120.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="78.33203125" customWidth="1"/>
     <col min="8" max="8" width="161.6640625" customWidth="1"/>
     <col min="9" max="9" width="187.33203125" customWidth="1"/>
@@ -1395,13 +1392,13 @@
   <sheetData>
     <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -1437,7 +1434,7 @@
         <v>10</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P1" t="s">
         <v>11</v>
@@ -1899,437 +1896,437 @@
       <c r="E12" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
         <v>136</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>137</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>138</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>139</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>140</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>141</v>
-      </c>
-      <c r="L12" t="s">
-        <v>142</v>
       </c>
       <c r="M12" t="s">
         <v>83</v>
       </c>
       <c r="N12" t="s">
+        <v>142</v>
+      </c>
+      <c r="P12" t="s">
         <v>143</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>144</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="S12" t="s">
         <v>146</v>
-      </c>
-      <c r="S12" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E13" t="s">
         <v>148</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>149</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>150</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" t="s">
         <v>152</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
+        <v>140</v>
+      </c>
+      <c r="L13" t="s">
         <v>153</v>
-      </c>
-      <c r="K13" t="s">
-        <v>141</v>
-      </c>
-      <c r="L13" t="s">
-        <v>154</v>
       </c>
       <c r="M13" t="s">
         <v>46</v>
       </c>
       <c r="N13" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q13" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="Q13" s="3" t="s">
+      <c r="R13" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="S13" t="s">
         <v>157</v>
-      </c>
-      <c r="S13" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
       </c>
       <c r="G14" t="s">
+        <v>160</v>
+      </c>
+      <c r="H14" t="s">
         <v>161</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>162</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>163</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
+        <v>140</v>
+      </c>
+      <c r="L14" t="s">
         <v>164</v>
-      </c>
-      <c r="K14" t="s">
-        <v>141</v>
-      </c>
-      <c r="L14" t="s">
-        <v>165</v>
       </c>
       <c r="M14" t="s">
         <v>83</v>
       </c>
       <c r="N14" t="s">
+        <v>165</v>
+      </c>
+      <c r="P14" t="s">
         <v>166</v>
       </c>
-      <c r="P14" t="s">
+      <c r="R14" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="S14" t="s">
         <v>168</v>
-      </c>
-      <c r="S14" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D15" t="s">
+        <v>169</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
       </c>
       <c r="G15" t="s">
+        <v>171</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" t="s">
         <v>173</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>174</v>
-      </c>
-      <c r="J15" t="s">
-        <v>175</v>
       </c>
       <c r="K15" t="s">
         <v>70</v>
       </c>
       <c r="L15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s">
         <v>46</v>
       </c>
       <c r="N15" t="s">
+        <v>176</v>
+      </c>
+      <c r="P15" t="s">
         <v>177</v>
       </c>
-      <c r="P15" t="s">
+      <c r="R15" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="R15" s="1" t="s">
+      <c r="S15" t="s">
         <v>179</v>
-      </c>
-      <c r="S15" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
+        <v>182</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" t="s">
         <v>184</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
+        <v>163</v>
+      </c>
+      <c r="K16" t="s">
+        <v>140</v>
+      </c>
+      <c r="L16" t="s">
         <v>185</v>
-      </c>
-      <c r="J16" t="s">
-        <v>164</v>
-      </c>
-      <c r="K16" t="s">
-        <v>141</v>
-      </c>
-      <c r="L16" t="s">
-        <v>186</v>
       </c>
       <c r="M16" t="s">
         <v>46</v>
       </c>
       <c r="N16" t="s">
+        <v>186</v>
+      </c>
+      <c r="P16" t="s">
         <v>187</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="Q16" s="3" t="s">
+      <c r="R16" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="S16" t="s">
         <v>190</v>
-      </c>
-      <c r="S16" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="17" spans="4:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D17" t="s">
+        <v>191</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" t="s">
         <v>192</v>
       </c>
-      <c r="F17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="H17" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" t="s">
         <v>194</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>195</v>
-      </c>
-      <c r="J17" t="s">
-        <v>196</v>
       </c>
       <c r="K17" t="s">
         <v>128</v>
       </c>
       <c r="L17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M17" t="s">
         <v>46</v>
       </c>
       <c r="N17" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q17" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="Q17" s="3" t="s">
+      <c r="R17" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="S17" t="s">
         <v>200</v>
-      </c>
-      <c r="S17" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="18" spans="4:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D18" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="F18" t="s">
         <v>17</v>
       </c>
       <c r="G18" t="s">
+        <v>203</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" t="s">
+        <v>184</v>
+      </c>
+      <c r="J18" t="s">
+        <v>163</v>
+      </c>
+      <c r="K18" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" t="s">
         <v>205</v>
-      </c>
-      <c r="I18" t="s">
-        <v>185</v>
-      </c>
-      <c r="J18" t="s">
-        <v>164</v>
-      </c>
-      <c r="K18" t="s">
-        <v>141</v>
-      </c>
-      <c r="L18" t="s">
-        <v>206</v>
       </c>
       <c r="M18" t="s">
         <v>46</v>
       </c>
       <c r="N18" t="s">
+        <v>206</v>
+      </c>
+      <c r="P18" t="s">
         <v>207</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="Q18" s="3" t="s">
+      <c r="R18" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="S18" t="s">
         <v>210</v>
-      </c>
-      <c r="S18" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="19" spans="4:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D19" t="s">
+        <v>211</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="F19" t="s">
         <v>17</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="I19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s">
         <v>83</v>
       </c>
       <c r="N19" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="Q19" s="3" t="s">
+      <c r="R19" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="S19" t="s">
         <v>218</v>
-      </c>
-      <c r="S19" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="20" spans="4:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D20" t="s">
+        <v>219</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
         <v>221</v>
       </c>
-      <c r="F20" t="s">
-        <v>136</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>222</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>223</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>224</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
+        <v>140</v>
+      </c>
+      <c r="L20" t="s">
         <v>225</v>
-      </c>
-      <c r="K20" t="s">
-        <v>141</v>
-      </c>
-      <c r="L20" t="s">
-        <v>226</v>
       </c>
       <c r="M20" t="s">
         <v>46</v>
       </c>
       <c r="N20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>107</v>
       </c>
       <c r="S20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="4:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D21" t="s">
+        <v>228</v>
+      </c>
+      <c r="E21" t="s">
         <v>229</v>
-      </c>
-      <c r="E21" t="s">
-        <v>230</v>
       </c>
       <c r="F21" t="s">
         <v>17</v>
       </c>
       <c r="G21" t="s">
+        <v>230</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" t="s">
         <v>232</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>233</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>234</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>235</v>
-      </c>
-      <c r="L21" t="s">
-        <v>236</v>
       </c>
       <c r="M21" t="s">
         <v>23</v>
       </c>
       <c r="N21" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q21" t="s">
         <v>237</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="R21" s="1" t="s">
+      <c r="S21" t="s">
         <v>239</v>
-      </c>
-      <c r="S21" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="22" spans="4:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
